--- a/TestFiles-prod-sanity/AdvanceAndRecovery/[MLB]AdvanceStatement-AR.xlsx
+++ b/TestFiles-prod-sanity/AdvanceAndRecovery/[MLB]AdvanceStatement-AR.xlsx
@@ -88,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>ATENA-ADV-AR-TEST-A039</t>
+    <t>ATENA-ADV-AR-TEST-A049</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -97,7 +97,7 @@
     <t>IL</t>
   </si>
   <si>
-    <t>test-aetna-aca-test-advance-month-july-21</t>
+    <t>test-aetna-aca-advance-july-21</t>
   </si>
   <si>
     <t>Y</t>
